--- a/backend/catalogues_src/Grade 8 Natural Sciences Catalogue.xlsx
+++ b/backend/catalogues_src/Grade 8 Natural Sciences Catalogue.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -190,8 +190,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -388,6 +394,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1018,7 +1030,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1222,6 +1234,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="34" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P176"/>
+  <dimension ref="B2:P176"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="33" min="1" max="1"/>
@@ -1628,7 +1649,6 @@
     <col width="18" customWidth="1" style="33" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="14.95" customHeight="1" s="33">
       <c r="B2" s="69" t="inlineStr">
         <is>
@@ -1642,7 +1662,13 @@
       <c r="G2" s="70" t="n"/>
       <c r="H2" s="70" t="n"/>
       <c r="I2" s="70" t="n"/>
-      <c r="J2" s="71" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="38" t="n"/>
@@ -2149,8 +2175,14 @@
       <c r="F24" s="70" t="n"/>
       <c r="G24" s="70" t="n"/>
       <c r="H24" s="70" t="n"/>
-      <c r="I24" s="71" t="n"/>
-      <c r="J24" s="58" t="n"/>
+      <c r="I24" s="70" t="n"/>
+      <c r="J24" s="70" t="n"/>
+      <c r="K24" s="70" t="n"/>
+      <c r="L24" s="70" t="n"/>
+      <c r="M24" s="70" t="n"/>
+      <c r="N24" s="70" t="n"/>
+      <c r="O24" s="70" t="n"/>
+      <c r="P24" s="71" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="38" t="n"/>
@@ -2675,7 +2707,13 @@
       <c r="G47" s="70" t="n"/>
       <c r="H47" s="70" t="n"/>
       <c r="I47" s="70" t="n"/>
-      <c r="J47" s="71" t="n"/>
+      <c r="J47" s="70" t="n"/>
+      <c r="K47" s="70" t="n"/>
+      <c r="L47" s="70" t="n"/>
+      <c r="M47" s="70" t="n"/>
+      <c r="N47" s="70" t="n"/>
+      <c r="O47" s="70" t="n"/>
+      <c r="P47" s="71" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="38" t="n"/>
@@ -3182,8 +3220,14 @@
       <c r="F69" s="70" t="n"/>
       <c r="G69" s="70" t="n"/>
       <c r="H69" s="70" t="n"/>
-      <c r="I69" s="71" t="n"/>
-      <c r="J69" s="58" t="n"/>
+      <c r="I69" s="70" t="n"/>
+      <c r="J69" s="70" t="n"/>
+      <c r="K69" s="70" t="n"/>
+      <c r="L69" s="70" t="n"/>
+      <c r="M69" s="70" t="n"/>
+      <c r="N69" s="70" t="n"/>
+      <c r="O69" s="70" t="n"/>
+      <c r="P69" s="71" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="38" t="n"/>
@@ -3708,7 +3752,13 @@
       <c r="G92" s="70" t="n"/>
       <c r="H92" s="70" t="n"/>
       <c r="I92" s="70" t="n"/>
-      <c r="J92" s="71" t="n"/>
+      <c r="J92" s="70" t="n"/>
+      <c r="K92" s="70" t="n"/>
+      <c r="L92" s="70" t="n"/>
+      <c r="M92" s="70" t="n"/>
+      <c r="N92" s="70" t="n"/>
+      <c r="O92" s="70" t="n"/>
+      <c r="P92" s="71" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="38" t="n"/>
@@ -4215,8 +4265,14 @@
       <c r="F114" s="70" t="n"/>
       <c r="G114" s="70" t="n"/>
       <c r="H114" s="70" t="n"/>
-      <c r="I114" s="71" t="n"/>
-      <c r="J114" s="58" t="n"/>
+      <c r="I114" s="70" t="n"/>
+      <c r="J114" s="70" t="n"/>
+      <c r="K114" s="70" t="n"/>
+      <c r="L114" s="70" t="n"/>
+      <c r="M114" s="70" t="n"/>
+      <c r="N114" s="70" t="n"/>
+      <c r="O114" s="70" t="n"/>
+      <c r="P114" s="71" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="38" t="n"/>
@@ -4724,7 +4780,13 @@
       <c r="G136" s="70" t="n"/>
       <c r="H136" s="70" t="n"/>
       <c r="I136" s="70" t="n"/>
-      <c r="J136" s="71" t="n"/>
+      <c r="J136" s="70" t="n"/>
+      <c r="K136" s="70" t="n"/>
+      <c r="L136" s="70" t="n"/>
+      <c r="M136" s="70" t="n"/>
+      <c r="N136" s="70" t="n"/>
+      <c r="O136" s="70" t="n"/>
+      <c r="P136" s="71" t="n"/>
     </row>
     <row r="137">
       <c r="B137" s="38" t="n"/>
@@ -5231,8 +5293,14 @@
       <c r="F158" s="70" t="n"/>
       <c r="G158" s="70" t="n"/>
       <c r="H158" s="70" t="n"/>
-      <c r="I158" s="71" t="n"/>
-      <c r="J158" s="58" t="n"/>
+      <c r="I158" s="70" t="n"/>
+      <c r="J158" s="70" t="n"/>
+      <c r="K158" s="70" t="n"/>
+      <c r="L158" s="70" t="n"/>
+      <c r="M158" s="70" t="n"/>
+      <c r="N158" s="70" t="n"/>
+      <c r="O158" s="70" t="n"/>
+      <c r="P158" s="71" t="n"/>
     </row>
     <row r="159">
       <c r="B159" s="38" t="n"/>
@@ -5678,62 +5746,62 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="J137:M137"/>
+    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="B2:P2"/>
     <mergeCell ref="N93:P93"/>
     <mergeCell ref="C137:C138"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="G115:I115"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="N159:P159"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="J137:M137"/>
-    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="G137:I137"/>
     <mergeCell ref="B3:B4"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="B136:P136"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J115:M115"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="B69:P69"/>
     <mergeCell ref="D137:F137"/>
+    <mergeCell ref="J159:M159"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="B48:B49"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="N137:P137"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C93:C94"/>
     <mergeCell ref="D3:F3"/>
+    <mergeCell ref="B158:P158"/>
     <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B92:P92"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="C70:C71"/>
     <mergeCell ref="J93:M93"/>
+    <mergeCell ref="B24:P24"/>
     <mergeCell ref="G159:I159"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="B114:I114"/>
-    <mergeCell ref="G137:I137"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="G93:I93"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="J159:M159"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="B92:J92"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="B114:P114"/>
+    <mergeCell ref="N70:P70"/>
     <mergeCell ref="D115:F115"/>
     <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="B158:I158"/>
+    <mergeCell ref="G115:I115"/>
     <mergeCell ref="N25:P25"/>
-    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="B47:P47"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="N159:P159"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="G70:I70"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="B159:B160"/>
     <mergeCell ref="J25:M25"/>
+    <mergeCell ref="B115:B116"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="N115:P115"/>
-    <mergeCell ref="B136:J136"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="J115:M115"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="B137:B138"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="B115:B116"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5776,9 +5844,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -6120,9 +6195,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -6464,9 +6546,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -6808,9 +6897,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -7152,9 +7248,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -7398,25 +7501,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7496,9 +7599,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -7742,25 +7852,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7840,9 +7950,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -8184,9 +8301,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -8537,61 +8661,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8634,9 +8758,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -8978,9 +9109,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -9322,9 +9460,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -9666,9 +9811,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -10010,9 +10162,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -10256,25 +10415,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10354,9 +10513,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -10600,25 +10766,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10698,9 +10864,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -11042,9 +11215,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -11379,61 +11559,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11445,7 +11625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:P25"/>
+  <dimension ref="B2:P25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.6238532110092" customWidth="1" style="1" min="2" max="23"/>
@@ -11476,11 +11656,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="H2" s="5" t="n"/>
-      <c r="I2" s="5" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -11750,11 +11935,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -12017,17 +12207,17 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
     <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="B15:B16"/>
@@ -12074,7 +12264,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -12195,37 +12394,37 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>1.8, 10</t>
+          <t>Q1.8, Q10</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.5, Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>1.9, 9</t>
+          <t>Q1.9, Q9</t>
         </is>
       </c>
       <c r="J5" s="22" t="n"/>
@@ -12275,37 +12474,37 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>1.9, 10</t>
+          <t>Q1.9, Q10</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 5</t>
+          <t>Q1.4, Q1.5, Q5</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
         <is>
-          <t>1.8, 9</t>
+          <t>Q1.8, Q9</t>
         </is>
       </c>
       <c r="J7" s="22" t="n"/>
@@ -12329,32 +12528,34 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.7, 10</t>
+          <t>Q1.1, Q1.7, Q10</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>1.3, 1.6, 11</t>
+          <t>Q1.3, Q1.6, Q11</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.4, 1.8, 2, 3, 4</t>
+          <t>Q1.2, Q1.4, Q1.8, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>1.5, 5</t>
+          <t>Q1.5, Q5</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>1.9, 1.10, 6, 7, 8</t>
+          <t>Q1.9, Q1.10, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n">
-        <v>9</v>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="J8" s="22" t="n"/>
       <c r="K8" s="22" t="n"/>
@@ -12494,7 +12695,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -12615,32 +12825,32 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2</t>
+          <t>Q1.2, Q1.3, Q2</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 1.6, 1.7,3, 4</t>
+          <t>Q1.4, Q1.5, Q1.6, Q1.7, Q3, Q4</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>1.8, 7, 8</t>
+          <t>Q1.8, Q7, Q8</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>1.9, 1.10, 9</t>
+          <t>Q1.9, Q1.10, Q9</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>Q5, Q6</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>1.1, 10</t>
+          <t>Q1.1, Q10</t>
         </is>
       </c>
       <c r="I17" s="22" t="n"/>
@@ -12691,32 +12901,32 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>1.6, 1.8, 2.6, 2.7</t>
+          <t>Q1.6, Q1.8, Q2.6, Q2.7</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 1.9, 2.1, 3, 4</t>
+          <t>Q1.3, Q1.4, Q1.5, Q1.9, Q2.1, Q3, Q4</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>5, 7, 8</t>
+          <t>Q5, Q7, Q8</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>1.7, 6</t>
+          <t>Q1.7, Q6</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>Q1.2</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.10, 9</t>
+          <t>Q1.1, Q1.10, Q9</t>
         </is>
       </c>
       <c r="I19" s="22" t="n"/>
@@ -12741,30 +12951,32 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>1.1, 1.6, 2, 3</t>
+          <t>Q1.1, Q1.6, Q2, Q3</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 1.5, 1.7, 4, 6</t>
+          <t>Q1.2, Q1.3, Q1.5, Q1.7, Q4, Q6</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>1.4, 1.9, 7, 8, (9.1-9.2)</t>
+          <t>Q1.4, Q1.9, Q7, Q8, Q9.1-9.2</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>1.8, 9.3</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>5</v>
+          <t>Q1.8, Q9.3</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>1.10, 10</t>
+          <t>Q1.10, Q10</t>
         </is>
       </c>
       <c r="I20" s="22" t="n"/>
@@ -12906,7 +13118,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -13020,25 +13241,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="79" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
+      <c r="C29" s="80" t="n"/>
+      <c r="D29" s="80" t="n"/>
+      <c r="E29" s="80" t="n"/>
+      <c r="F29" s="80" t="n"/>
+      <c r="G29" s="80" t="n"/>
+      <c r="H29" s="80" t="n"/>
+      <c r="I29" s="80" t="n"/>
+      <c r="J29" s="80" t="n"/>
+      <c r="K29" s="80" t="n"/>
+      <c r="L29" s="80" t="n"/>
+      <c r="M29" s="80" t="n"/>
+      <c r="N29" s="80" t="n"/>
+      <c r="O29" s="80" t="n"/>
+      <c r="P29" s="80" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13053,36 +13274,38 @@
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>1.9, 10</t>
+          <t>Q1.9, Q10</t>
         </is>
       </c>
       <c r="D30" s="31" t="inlineStr">
         <is>
-          <t>1.10, 11</t>
+          <t>Q1.10, Q11</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3, 4</t>
+          <t>Q1.2, Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F30" s="31" t="inlineStr">
         <is>
-          <t>1.8, 5</t>
+          <t>Q1.8, Q5</t>
         </is>
       </c>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>1.4, 1.5, 1.6, 6, 7, 8</t>
+          <t>Q1.4, Q1.5, Q1.6, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.7</t>
-        </is>
-      </c>
-      <c r="I30" s="31" t="n">
-        <v>9</v>
+          <t>Q1.1, Q1.7</t>
+        </is>
+      </c>
+      <c r="I30" s="31" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="J30" s="31" t="n"/>
       <c r="K30" s="31" t="n"/>
@@ -13098,25 +13321,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="79" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
+      <c r="C31" s="80" t="n"/>
+      <c r="D31" s="80" t="n"/>
+      <c r="E31" s="80" t="n"/>
+      <c r="F31" s="80" t="n"/>
+      <c r="G31" s="80" t="n"/>
+      <c r="H31" s="80" t="n"/>
+      <c r="I31" s="80" t="n"/>
+      <c r="J31" s="80" t="n"/>
+      <c r="K31" s="80" t="n"/>
+      <c r="L31" s="80" t="n"/>
+      <c r="M31" s="80" t="n"/>
+      <c r="N31" s="80" t="n"/>
+      <c r="O31" s="80" t="n"/>
+      <c r="P31" s="80" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13124,25 +13347,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="79" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
+      <c r="C32" s="80" t="n"/>
+      <c r="D32" s="80" t="n"/>
+      <c r="E32" s="80" t="n"/>
+      <c r="F32" s="80" t="n"/>
+      <c r="G32" s="80" t="n"/>
+      <c r="H32" s="80" t="n"/>
+      <c r="I32" s="80" t="n"/>
+      <c r="J32" s="80" t="n"/>
+      <c r="K32" s="80" t="n"/>
+      <c r="L32" s="80" t="n"/>
+      <c r="M32" s="80" t="n"/>
+      <c r="N32" s="80" t="n"/>
+      <c r="O32" s="80" t="n"/>
+      <c r="P32" s="80" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13150,25 +13373,25 @@
           <t>y</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="79" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
+      <c r="C33" s="80" t="n"/>
+      <c r="D33" s="80" t="n"/>
+      <c r="E33" s="80" t="n"/>
+      <c r="F33" s="80" t="n"/>
+      <c r="G33" s="80" t="n"/>
+      <c r="H33" s="80" t="n"/>
+      <c r="I33" s="80" t="n"/>
+      <c r="J33" s="80" t="n"/>
+      <c r="K33" s="80" t="n"/>
+      <c r="L33" s="80" t="n"/>
+      <c r="M33" s="80" t="n"/>
+      <c r="N33" s="80" t="n"/>
+      <c r="O33" s="80" t="n"/>
+      <c r="P33" s="80" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -13176,25 +13399,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
+      <c r="C34" s="80" t="n"/>
+      <c r="D34" s="80" t="n"/>
+      <c r="E34" s="80" t="n"/>
+      <c r="F34" s="80" t="n"/>
+      <c r="G34" s="80" t="n"/>
+      <c r="H34" s="80" t="n"/>
+      <c r="I34" s="80" t="n"/>
+      <c r="J34" s="80" t="n"/>
+      <c r="K34" s="80" t="n"/>
+      <c r="L34" s="80" t="n"/>
+      <c r="M34" s="80" t="n"/>
+      <c r="N34" s="80" t="n"/>
+      <c r="O34" s="80" t="n"/>
+      <c r="P34" s="80" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -13202,25 +13425,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
+      <c r="C35" s="80" t="n"/>
+      <c r="D35" s="80" t="n"/>
+      <c r="E35" s="80" t="n"/>
+      <c r="F35" s="80" t="n"/>
+      <c r="G35" s="80" t="n"/>
+      <c r="H35" s="80" t="n"/>
+      <c r="I35" s="80" t="n"/>
+      <c r="J35" s="80" t="n"/>
+      <c r="K35" s="80" t="n"/>
+      <c r="L35" s="80" t="n"/>
+      <c r="M35" s="80" t="n"/>
+      <c r="N35" s="80" t="n"/>
+      <c r="O35" s="80" t="n"/>
+      <c r="P35" s="80" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="33">
       <c r="A36" t="inlineStr">
@@ -13228,25 +13451,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
+      <c r="C36" s="80" t="n"/>
+      <c r="D36" s="80" t="n"/>
+      <c r="E36" s="80" t="n"/>
+      <c r="F36" s="80" t="n"/>
+      <c r="G36" s="80" t="n"/>
+      <c r="H36" s="80" t="n"/>
+      <c r="I36" s="80" t="n"/>
+      <c r="J36" s="80" t="n"/>
+      <c r="K36" s="80" t="n"/>
+      <c r="L36" s="80" t="n"/>
+      <c r="M36" s="80" t="n"/>
+      <c r="N36" s="80" t="n"/>
+      <c r="O36" s="80" t="n"/>
+      <c r="P36" s="80" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="33">
       <c r="C37" s="31" t="n"/>
@@ -13274,7 +13497,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -13388,25 +13620,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="21" t="n"/>
-      <c r="P41" s="21" t="n"/>
+      <c r="C41" s="82" t="n"/>
+      <c r="D41" s="82" t="n"/>
+      <c r="E41" s="82" t="n"/>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="82" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
+      <c r="L41" s="82" t="n"/>
+      <c r="M41" s="82" t="n"/>
+      <c r="N41" s="82" t="n"/>
+      <c r="O41" s="82" t="n"/>
+      <c r="P41" s="82" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -13421,28 +13653,28 @@
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 2, 3</t>
+          <t>Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.4, 1.5, 1.6, 1.7, 1.9, 4, 5</t>
+          <t>Q1.1, Q1.4, Q1.5, Q1.6, Q1.7, Q1.9, Q4, Q5</t>
         </is>
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>7 ,(10.1-10.2)</t>
+          <t>Q7, Q10.1-10.2</t>
         </is>
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>1.8, 6, 8, 9</t>
+          <t>Q1.8, Q6, Q8, Q9</t>
         </is>
       </c>
       <c r="G42" s="21" t="n"/>
       <c r="H42" s="21" t="inlineStr">
         <is>
-          <t>1.10, (10.3-10.5)</t>
+          <t>Q1.10, Q10.3-10.5</t>
         </is>
       </c>
       <c r="I42" s="21" t="n"/>
@@ -13460,25 +13692,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="21" t="n"/>
-      <c r="P43" s="21" t="n"/>
+      <c r="C43" s="82" t="n"/>
+      <c r="D43" s="82" t="n"/>
+      <c r="E43" s="82" t="n"/>
+      <c r="F43" s="82" t="n"/>
+      <c r="G43" s="82" t="n"/>
+      <c r="H43" s="82" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
+      <c r="L43" s="82" t="n"/>
+      <c r="M43" s="82" t="n"/>
+      <c r="N43" s="82" t="n"/>
+      <c r="O43" s="82" t="n"/>
+      <c r="P43" s="82" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -13486,25 +13718,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="21" t="n"/>
-      <c r="P44" s="21" t="n"/>
+      <c r="C44" s="82" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="82" t="n"/>
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="82" t="n"/>
+      <c r="H44" s="82" t="n"/>
+      <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="n"/>
+      <c r="K44" s="82" t="n"/>
+      <c r="L44" s="82" t="n"/>
+      <c r="M44" s="82" t="n"/>
+      <c r="N44" s="82" t="n"/>
+      <c r="O44" s="82" t="n"/>
+      <c r="P44" s="82" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13512,25 +13744,25 @@
           <t>y</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="21" t="n"/>
-      <c r="P45" s="21" t="n"/>
+      <c r="C45" s="82" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="82" t="n"/>
+      <c r="F45" s="82" t="n"/>
+      <c r="G45" s="82" t="n"/>
+      <c r="H45" s="82" t="n"/>
+      <c r="I45" s="82" t="n"/>
+      <c r="J45" s="82" t="n"/>
+      <c r="K45" s="82" t="n"/>
+      <c r="L45" s="82" t="n"/>
+      <c r="M45" s="82" t="n"/>
+      <c r="N45" s="82" t="n"/>
+      <c r="O45" s="82" t="n"/>
+      <c r="P45" s="82" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13538,25 +13770,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="79" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="21" t="n"/>
-      <c r="P46" s="21" t="n"/>
+      <c r="C46" s="82" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="82" t="n"/>
+      <c r="F46" s="82" t="n"/>
+      <c r="G46" s="82" t="n"/>
+      <c r="H46" s="82" t="n"/>
+      <c r="I46" s="82" t="n"/>
+      <c r="J46" s="82" t="n"/>
+      <c r="K46" s="82" t="n"/>
+      <c r="L46" s="82" t="n"/>
+      <c r="M46" s="82" t="n"/>
+      <c r="N46" s="82" t="n"/>
+      <c r="O46" s="82" t="n"/>
+      <c r="P46" s="82" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13564,25 +13796,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="79" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
-      <c r="P47" s="21" t="n"/>
+      <c r="C47" s="82" t="n"/>
+      <c r="D47" s="82" t="n"/>
+      <c r="E47" s="82" t="n"/>
+      <c r="F47" s="82" t="n"/>
+      <c r="G47" s="82" t="n"/>
+      <c r="H47" s="82" t="n"/>
+      <c r="I47" s="82" t="n"/>
+      <c r="J47" s="82" t="n"/>
+      <c r="K47" s="82" t="n"/>
+      <c r="L47" s="82" t="n"/>
+      <c r="M47" s="82" t="n"/>
+      <c r="N47" s="82" t="n"/>
+      <c r="O47" s="82" t="n"/>
+      <c r="P47" s="82" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="33">
       <c r="A48" t="inlineStr">
@@ -13590,25 +13822,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B48" s="81" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-      <c r="P48" s="21" t="n"/>
+      <c r="C48" s="82" t="n"/>
+      <c r="D48" s="82" t="n"/>
+      <c r="E48" s="82" t="n"/>
+      <c r="F48" s="82" t="n"/>
+      <c r="G48" s="82" t="n"/>
+      <c r="H48" s="82" t="n"/>
+      <c r="I48" s="82" t="n"/>
+      <c r="J48" s="82" t="n"/>
+      <c r="K48" s="82" t="n"/>
+      <c r="L48" s="82" t="n"/>
+      <c r="M48" s="82" t="n"/>
+      <c r="N48" s="82" t="n"/>
+      <c r="O48" s="82" t="n"/>
+      <c r="P48" s="82" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="33">
       <c r="C49" s="21" t="n"/>
@@ -13636,7 +13868,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -13750,25 +13991,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C53" s="31" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="31" t="n"/>
-      <c r="F53" s="31" t="n"/>
-      <c r="G53" s="31" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="31" t="n"/>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="31" t="n"/>
-      <c r="L53" s="31" t="n"/>
-      <c r="M53" s="31" t="n"/>
-      <c r="N53" s="31" t="n"/>
-      <c r="O53" s="31" t="n"/>
-      <c r="P53" s="31" t="n"/>
+      <c r="C53" s="80" t="n"/>
+      <c r="D53" s="80" t="n"/>
+      <c r="E53" s="80" t="n"/>
+      <c r="F53" s="80" t="n"/>
+      <c r="G53" s="80" t="n"/>
+      <c r="H53" s="80" t="n"/>
+      <c r="I53" s="80" t="n"/>
+      <c r="J53" s="80" t="n"/>
+      <c r="K53" s="80" t="n"/>
+      <c r="L53" s="80" t="n"/>
+      <c r="M53" s="80" t="n"/>
+      <c r="N53" s="80" t="n"/>
+      <c r="O53" s="80" t="n"/>
+      <c r="P53" s="80" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13776,25 +14017,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="31" t="n"/>
-      <c r="D54" s="31" t="n"/>
-      <c r="E54" s="31" t="n"/>
-      <c r="F54" s="31" t="n"/>
-      <c r="G54" s="31" t="n"/>
-      <c r="H54" s="31" t="n"/>
-      <c r="I54" s="31" t="n"/>
-      <c r="J54" s="31" t="n"/>
-      <c r="K54" s="31" t="n"/>
-      <c r="L54" s="31" t="n"/>
-      <c r="M54" s="31" t="n"/>
-      <c r="N54" s="31" t="n"/>
-      <c r="O54" s="31" t="n"/>
-      <c r="P54" s="31" t="n"/>
+      <c r="C54" s="80" t="n"/>
+      <c r="D54" s="80" t="n"/>
+      <c r="E54" s="80" t="n"/>
+      <c r="F54" s="80" t="n"/>
+      <c r="G54" s="80" t="n"/>
+      <c r="H54" s="80" t="n"/>
+      <c r="I54" s="80" t="n"/>
+      <c r="J54" s="80" t="n"/>
+      <c r="K54" s="80" t="n"/>
+      <c r="L54" s="80" t="n"/>
+      <c r="M54" s="80" t="n"/>
+      <c r="N54" s="80" t="n"/>
+      <c r="O54" s="80" t="n"/>
+      <c r="P54" s="80" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13802,25 +14043,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C55" s="31" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="31" t="n"/>
-      <c r="F55" s="31" t="n"/>
-      <c r="G55" s="31" t="n"/>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="31" t="n"/>
-      <c r="J55" s="31" t="n"/>
-      <c r="K55" s="31" t="n"/>
-      <c r="L55" s="31" t="n"/>
-      <c r="M55" s="31" t="n"/>
-      <c r="N55" s="31" t="n"/>
-      <c r="O55" s="31" t="n"/>
-      <c r="P55" s="31" t="n"/>
+      <c r="C55" s="80" t="n"/>
+      <c r="D55" s="80" t="n"/>
+      <c r="E55" s="80" t="n"/>
+      <c r="F55" s="80" t="n"/>
+      <c r="G55" s="80" t="n"/>
+      <c r="H55" s="80" t="n"/>
+      <c r="I55" s="80" t="n"/>
+      <c r="J55" s="80" t="n"/>
+      <c r="K55" s="80" t="n"/>
+      <c r="L55" s="80" t="n"/>
+      <c r="M55" s="80" t="n"/>
+      <c r="N55" s="80" t="n"/>
+      <c r="O55" s="80" t="n"/>
+      <c r="P55" s="80" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -13828,25 +14069,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B56" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C56" s="31" t="n"/>
-      <c r="D56" s="31" t="n"/>
-      <c r="E56" s="31" t="n"/>
-      <c r="F56" s="31" t="n"/>
-      <c r="G56" s="31" t="n"/>
-      <c r="H56" s="31" t="n"/>
-      <c r="I56" s="31" t="n"/>
-      <c r="J56" s="31" t="n"/>
-      <c r="K56" s="31" t="n"/>
-      <c r="L56" s="31" t="n"/>
-      <c r="M56" s="31" t="n"/>
-      <c r="N56" s="31" t="n"/>
-      <c r="O56" s="31" t="n"/>
-      <c r="P56" s="31" t="n"/>
+      <c r="C56" s="80" t="n"/>
+      <c r="D56" s="80" t="n"/>
+      <c r="E56" s="80" t="n"/>
+      <c r="F56" s="80" t="n"/>
+      <c r="G56" s="80" t="n"/>
+      <c r="H56" s="80" t="n"/>
+      <c r="I56" s="80" t="n"/>
+      <c r="J56" s="80" t="n"/>
+      <c r="K56" s="80" t="n"/>
+      <c r="L56" s="80" t="n"/>
+      <c r="M56" s="80" t="n"/>
+      <c r="N56" s="80" t="n"/>
+      <c r="O56" s="80" t="n"/>
+      <c r="P56" s="80" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13854,25 +14095,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C57" s="31" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="31" t="n"/>
-      <c r="G57" s="31" t="n"/>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="31" t="n"/>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="31" t="n"/>
-      <c r="L57" s="31" t="n"/>
-      <c r="M57" s="31" t="n"/>
-      <c r="N57" s="31" t="n"/>
-      <c r="O57" s="31" t="n"/>
-      <c r="P57" s="31" t="n"/>
+      <c r="C57" s="80" t="n"/>
+      <c r="D57" s="80" t="n"/>
+      <c r="E57" s="80" t="n"/>
+      <c r="F57" s="80" t="n"/>
+      <c r="G57" s="80" t="n"/>
+      <c r="H57" s="80" t="n"/>
+      <c r="I57" s="80" t="n"/>
+      <c r="J57" s="80" t="n"/>
+      <c r="K57" s="80" t="n"/>
+      <c r="L57" s="80" t="n"/>
+      <c r="M57" s="80" t="n"/>
+      <c r="N57" s="80" t="n"/>
+      <c r="O57" s="80" t="n"/>
+      <c r="P57" s="80" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13880,25 +14121,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -13906,25 +14147,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B59" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C59" s="31" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="31" t="n"/>
-      <c r="F59" s="31" t="n"/>
-      <c r="G59" s="31" t="n"/>
-      <c r="H59" s="31" t="n"/>
-      <c r="I59" s="31" t="n"/>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="31" t="n"/>
-      <c r="L59" s="31" t="n"/>
-      <c r="M59" s="31" t="n"/>
-      <c r="N59" s="31" t="n"/>
-      <c r="O59" s="31" t="n"/>
-      <c r="P59" s="31" t="n"/>
+      <c r="C59" s="80" t="n"/>
+      <c r="D59" s="80" t="n"/>
+      <c r="E59" s="80" t="n"/>
+      <c r="F59" s="80" t="n"/>
+      <c r="G59" s="80" t="n"/>
+      <c r="H59" s="80" t="n"/>
+      <c r="I59" s="80" t="n"/>
+      <c r="J59" s="80" t="n"/>
+      <c r="K59" s="80" t="n"/>
+      <c r="L59" s="80" t="n"/>
+      <c r="M59" s="80" t="n"/>
+      <c r="N59" s="80" t="n"/>
+      <c r="O59" s="80" t="n"/>
+      <c r="P59" s="80" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="33">
       <c r="A60" t="inlineStr">
@@ -13932,25 +14173,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B60" s="28" t="inlineStr">
+      <c r="B60" s="81" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="31" t="n"/>
-      <c r="D60" s="31" t="n"/>
-      <c r="E60" s="31" t="n"/>
-      <c r="F60" s="31" t="n"/>
-      <c r="G60" s="31" t="n"/>
-      <c r="H60" s="31" t="n"/>
-      <c r="I60" s="31" t="n"/>
-      <c r="J60" s="31" t="n"/>
-      <c r="K60" s="31" t="n"/>
-      <c r="L60" s="31" t="n"/>
-      <c r="M60" s="31" t="n"/>
-      <c r="N60" s="31" t="n"/>
-      <c r="O60" s="31" t="n"/>
-      <c r="P60" s="31" t="n"/>
+      <c r="C60" s="80" t="n"/>
+      <c r="D60" s="80" t="n"/>
+      <c r="E60" s="80" t="n"/>
+      <c r="F60" s="80" t="n"/>
+      <c r="G60" s="80" t="n"/>
+      <c r="H60" s="80" t="n"/>
+      <c r="I60" s="80" t="n"/>
+      <c r="J60" s="80" t="n"/>
+      <c r="K60" s="80" t="n"/>
+      <c r="L60" s="80" t="n"/>
+      <c r="M60" s="80" t="n"/>
+      <c r="N60" s="80" t="n"/>
+      <c r="O60" s="80" t="n"/>
+      <c r="P60" s="80" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="33">
       <c r="C61" s="31" t="n"/>
@@ -13978,7 +14219,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -14092,25 +14342,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B65" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
-      <c r="J65" s="21" t="n"/>
-      <c r="K65" s="21" t="n"/>
-      <c r="L65" s="21" t="n"/>
-      <c r="M65" s="21" t="n"/>
-      <c r="N65" s="21" t="n"/>
-      <c r="O65" s="21" t="n"/>
-      <c r="P65" s="21" t="n"/>
+      <c r="C65" s="82" t="n"/>
+      <c r="D65" s="82" t="n"/>
+      <c r="E65" s="82" t="n"/>
+      <c r="F65" s="82" t="n"/>
+      <c r="G65" s="82" t="n"/>
+      <c r="H65" s="82" t="n"/>
+      <c r="I65" s="82" t="n"/>
+      <c r="J65" s="82" t="n"/>
+      <c r="K65" s="82" t="n"/>
+      <c r="L65" s="82" t="n"/>
+      <c r="M65" s="82" t="n"/>
+      <c r="N65" s="82" t="n"/>
+      <c r="O65" s="82" t="n"/>
+      <c r="P65" s="82" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -14118,25 +14368,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-      <c r="J66" s="21" t="n"/>
-      <c r="K66" s="21" t="n"/>
-      <c r="L66" s="21" t="n"/>
-      <c r="M66" s="21" t="n"/>
-      <c r="N66" s="21" t="n"/>
-      <c r="O66" s="21" t="n"/>
-      <c r="P66" s="21" t="n"/>
+      <c r="C66" s="82" t="n"/>
+      <c r="D66" s="82" t="n"/>
+      <c r="E66" s="82" t="n"/>
+      <c r="F66" s="82" t="n"/>
+      <c r="G66" s="82" t="n"/>
+      <c r="H66" s="82" t="n"/>
+      <c r="I66" s="82" t="n"/>
+      <c r="J66" s="82" t="n"/>
+      <c r="K66" s="82" t="n"/>
+      <c r="L66" s="82" t="n"/>
+      <c r="M66" s="82" t="n"/>
+      <c r="N66" s="82" t="n"/>
+      <c r="O66" s="82" t="n"/>
+      <c r="P66" s="82" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -14144,25 +14394,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n"/>
-      <c r="D67" s="21" t="n"/>
-      <c r="E67" s="21" t="n"/>
-      <c r="F67" s="21" t="n"/>
-      <c r="G67" s="21" t="n"/>
-      <c r="H67" s="21" t="n"/>
-      <c r="I67" s="21" t="n"/>
-      <c r="J67" s="21" t="n"/>
-      <c r="K67" s="21" t="n"/>
-      <c r="L67" s="21" t="n"/>
-      <c r="M67" s="21" t="n"/>
-      <c r="N67" s="21" t="n"/>
-      <c r="O67" s="21" t="n"/>
-      <c r="P67" s="21" t="n"/>
+      <c r="C67" s="82" t="n"/>
+      <c r="D67" s="82" t="n"/>
+      <c r="E67" s="82" t="n"/>
+      <c r="F67" s="82" t="n"/>
+      <c r="G67" s="82" t="n"/>
+      <c r="H67" s="82" t="n"/>
+      <c r="I67" s="82" t="n"/>
+      <c r="J67" s="82" t="n"/>
+      <c r="K67" s="82" t="n"/>
+      <c r="L67" s="82" t="n"/>
+      <c r="M67" s="82" t="n"/>
+      <c r="N67" s="82" t="n"/>
+      <c r="O67" s="82" t="n"/>
+      <c r="P67" s="82" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -14170,25 +14420,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B68" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-      <c r="J68" s="21" t="n"/>
-      <c r="K68" s="21" t="n"/>
-      <c r="L68" s="21" t="n"/>
-      <c r="M68" s="21" t="n"/>
-      <c r="N68" s="21" t="n"/>
-      <c r="O68" s="21" t="n"/>
-      <c r="P68" s="21" t="n"/>
+      <c r="C68" s="82" t="n"/>
+      <c r="D68" s="82" t="n"/>
+      <c r="E68" s="82" t="n"/>
+      <c r="F68" s="82" t="n"/>
+      <c r="G68" s="82" t="n"/>
+      <c r="H68" s="82" t="n"/>
+      <c r="I68" s="82" t="n"/>
+      <c r="J68" s="82" t="n"/>
+      <c r="K68" s="82" t="n"/>
+      <c r="L68" s="82" t="n"/>
+      <c r="M68" s="82" t="n"/>
+      <c r="N68" s="82" t="n"/>
+      <c r="O68" s="82" t="n"/>
+      <c r="P68" s="82" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -14196,25 +14446,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B69" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
-      <c r="J69" s="21" t="n"/>
-      <c r="K69" s="21" t="n"/>
-      <c r="L69" s="21" t="n"/>
-      <c r="M69" s="21" t="n"/>
-      <c r="N69" s="21" t="n"/>
-      <c r="O69" s="21" t="n"/>
-      <c r="P69" s="21" t="n"/>
+      <c r="C69" s="82" t="n"/>
+      <c r="D69" s="82" t="n"/>
+      <c r="E69" s="82" t="n"/>
+      <c r="F69" s="82" t="n"/>
+      <c r="G69" s="82" t="n"/>
+      <c r="H69" s="82" t="n"/>
+      <c r="I69" s="82" t="n"/>
+      <c r="J69" s="82" t="n"/>
+      <c r="K69" s="82" t="n"/>
+      <c r="L69" s="82" t="n"/>
+      <c r="M69" s="82" t="n"/>
+      <c r="N69" s="82" t="n"/>
+      <c r="O69" s="82" t="n"/>
+      <c r="P69" s="82" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -14222,25 +14472,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -14248,25 +14498,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B71" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-      <c r="J71" s="21" t="n"/>
-      <c r="K71" s="21" t="n"/>
-      <c r="L71" s="21" t="n"/>
-      <c r="M71" s="21" t="n"/>
-      <c r="N71" s="21" t="n"/>
-      <c r="O71" s="21" t="n"/>
-      <c r="P71" s="21" t="n"/>
+      <c r="C71" s="82" t="n"/>
+      <c r="D71" s="82" t="n"/>
+      <c r="E71" s="82" t="n"/>
+      <c r="F71" s="82" t="n"/>
+      <c r="G71" s="82" t="n"/>
+      <c r="H71" s="82" t="n"/>
+      <c r="I71" s="82" t="n"/>
+      <c r="J71" s="82" t="n"/>
+      <c r="K71" s="82" t="n"/>
+      <c r="L71" s="82" t="n"/>
+      <c r="M71" s="82" t="n"/>
+      <c r="N71" s="82" t="n"/>
+      <c r="O71" s="82" t="n"/>
+      <c r="P71" s="82" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="33">
       <c r="A72" t="inlineStr">
@@ -14274,25 +14524,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B72" s="28" t="inlineStr">
+      <c r="B72" s="81" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-      <c r="J72" s="21" t="n"/>
-      <c r="K72" s="21" t="n"/>
-      <c r="L72" s="21" t="n"/>
-      <c r="M72" s="21" t="n"/>
-      <c r="N72" s="21" t="n"/>
-      <c r="O72" s="21" t="n"/>
-      <c r="P72" s="21" t="n"/>
+      <c r="C72" s="82" t="n"/>
+      <c r="D72" s="82" t="n"/>
+      <c r="E72" s="82" t="n"/>
+      <c r="F72" s="82" t="n"/>
+      <c r="G72" s="82" t="n"/>
+      <c r="H72" s="82" t="n"/>
+      <c r="I72" s="82" t="n"/>
+      <c r="J72" s="82" t="n"/>
+      <c r="K72" s="82" t="n"/>
+      <c r="L72" s="82" t="n"/>
+      <c r="M72" s="82" t="n"/>
+      <c r="N72" s="82" t="n"/>
+      <c r="O72" s="82" t="n"/>
+      <c r="P72" s="82" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="33">
       <c r="C73" s="21" t="n"/>
@@ -14320,7 +14570,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -14434,25 +14693,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C77" s="31" t="n"/>
-      <c r="D77" s="31" t="n"/>
-      <c r="E77" s="31" t="n"/>
-      <c r="F77" s="31" t="n"/>
-      <c r="G77" s="31" t="n"/>
-      <c r="H77" s="31" t="n"/>
-      <c r="I77" s="31" t="n"/>
-      <c r="J77" s="31" t="n"/>
-      <c r="K77" s="31" t="n"/>
-      <c r="L77" s="31" t="n"/>
-      <c r="M77" s="31" t="n"/>
-      <c r="N77" s="31" t="n"/>
-      <c r="O77" s="31" t="n"/>
-      <c r="P77" s="31" t="n"/>
+      <c r="C77" s="80" t="n"/>
+      <c r="D77" s="80" t="n"/>
+      <c r="E77" s="80" t="n"/>
+      <c r="F77" s="80" t="n"/>
+      <c r="G77" s="80" t="n"/>
+      <c r="H77" s="80" t="n"/>
+      <c r="I77" s="80" t="n"/>
+      <c r="J77" s="80" t="n"/>
+      <c r="K77" s="80" t="n"/>
+      <c r="L77" s="80" t="n"/>
+      <c r="M77" s="80" t="n"/>
+      <c r="N77" s="80" t="n"/>
+      <c r="O77" s="80" t="n"/>
+      <c r="P77" s="80" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14460,25 +14719,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B78" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="31" t="n"/>
-      <c r="D78" s="31" t="n"/>
-      <c r="E78" s="31" t="n"/>
-      <c r="F78" s="31" t="n"/>
-      <c r="G78" s="31" t="n"/>
-      <c r="H78" s="31" t="n"/>
-      <c r="I78" s="31" t="n"/>
-      <c r="J78" s="31" t="n"/>
-      <c r="K78" s="31" t="n"/>
-      <c r="L78" s="31" t="n"/>
-      <c r="M78" s="31" t="n"/>
-      <c r="N78" s="31" t="n"/>
-      <c r="O78" s="31" t="n"/>
-      <c r="P78" s="31" t="n"/>
+      <c r="C78" s="80" t="n"/>
+      <c r="D78" s="80" t="n"/>
+      <c r="E78" s="80" t="n"/>
+      <c r="F78" s="80" t="n"/>
+      <c r="G78" s="80" t="n"/>
+      <c r="H78" s="80" t="n"/>
+      <c r="I78" s="80" t="n"/>
+      <c r="J78" s="80" t="n"/>
+      <c r="K78" s="80" t="n"/>
+      <c r="L78" s="80" t="n"/>
+      <c r="M78" s="80" t="n"/>
+      <c r="N78" s="80" t="n"/>
+      <c r="O78" s="80" t="n"/>
+      <c r="P78" s="80" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14486,25 +14745,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C79" s="31" t="n"/>
-      <c r="D79" s="31" t="n"/>
-      <c r="E79" s="31" t="n"/>
-      <c r="F79" s="31" t="n"/>
-      <c r="G79" s="31" t="n"/>
-      <c r="H79" s="31" t="n"/>
-      <c r="I79" s="31" t="n"/>
-      <c r="J79" s="31" t="n"/>
-      <c r="K79" s="31" t="n"/>
-      <c r="L79" s="31" t="n"/>
-      <c r="M79" s="31" t="n"/>
-      <c r="N79" s="31" t="n"/>
-      <c r="O79" s="31" t="n"/>
-      <c r="P79" s="31" t="n"/>
+      <c r="C79" s="80" t="n"/>
+      <c r="D79" s="80" t="n"/>
+      <c r="E79" s="80" t="n"/>
+      <c r="F79" s="80" t="n"/>
+      <c r="G79" s="80" t="n"/>
+      <c r="H79" s="80" t="n"/>
+      <c r="I79" s="80" t="n"/>
+      <c r="J79" s="80" t="n"/>
+      <c r="K79" s="80" t="n"/>
+      <c r="L79" s="80" t="n"/>
+      <c r="M79" s="80" t="n"/>
+      <c r="N79" s="80" t="n"/>
+      <c r="O79" s="80" t="n"/>
+      <c r="P79" s="80" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14512,25 +14771,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-      <c r="G80" s="31" t="n"/>
-      <c r="H80" s="31" t="n"/>
-      <c r="I80" s="31" t="n"/>
-      <c r="J80" s="31" t="n"/>
-      <c r="K80" s="31" t="n"/>
-      <c r="L80" s="31" t="n"/>
-      <c r="M80" s="31" t="n"/>
-      <c r="N80" s="31" t="n"/>
-      <c r="O80" s="31" t="n"/>
-      <c r="P80" s="31" t="n"/>
+      <c r="C80" s="80" t="n"/>
+      <c r="D80" s="80" t="n"/>
+      <c r="E80" s="80" t="n"/>
+      <c r="F80" s="80" t="n"/>
+      <c r="G80" s="80" t="n"/>
+      <c r="H80" s="80" t="n"/>
+      <c r="I80" s="80" t="n"/>
+      <c r="J80" s="80" t="n"/>
+      <c r="K80" s="80" t="n"/>
+      <c r="L80" s="80" t="n"/>
+      <c r="M80" s="80" t="n"/>
+      <c r="N80" s="80" t="n"/>
+      <c r="O80" s="80" t="n"/>
+      <c r="P80" s="80" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14538,25 +14797,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C81" s="31" t="n"/>
-      <c r="D81" s="31" t="n"/>
-      <c r="E81" s="31" t="n"/>
-      <c r="F81" s="31" t="n"/>
-      <c r="G81" s="31" t="n"/>
-      <c r="H81" s="31" t="n"/>
-      <c r="I81" s="31" t="n"/>
-      <c r="J81" s="31" t="n"/>
-      <c r="K81" s="31" t="n"/>
-      <c r="L81" s="31" t="n"/>
-      <c r="M81" s="31" t="n"/>
-      <c r="N81" s="31" t="n"/>
-      <c r="O81" s="31" t="n"/>
-      <c r="P81" s="31" t="n"/>
+      <c r="C81" s="80" t="n"/>
+      <c r="D81" s="80" t="n"/>
+      <c r="E81" s="80" t="n"/>
+      <c r="F81" s="80" t="n"/>
+      <c r="G81" s="80" t="n"/>
+      <c r="H81" s="80" t="n"/>
+      <c r="I81" s="80" t="n"/>
+      <c r="J81" s="80" t="n"/>
+      <c r="K81" s="80" t="n"/>
+      <c r="L81" s="80" t="n"/>
+      <c r="M81" s="80" t="n"/>
+      <c r="N81" s="80" t="n"/>
+      <c r="O81" s="80" t="n"/>
+      <c r="P81" s="80" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14564,25 +14823,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B82" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C82" s="31" t="n"/>
-      <c r="D82" s="31" t="n"/>
-      <c r="E82" s="31" t="n"/>
-      <c r="F82" s="31" t="n"/>
-      <c r="G82" s="31" t="n"/>
-      <c r="H82" s="31" t="n"/>
-      <c r="I82" s="31" t="n"/>
-      <c r="J82" s="31" t="n"/>
-      <c r="K82" s="31" t="n"/>
-      <c r="L82" s="31" t="n"/>
-      <c r="M82" s="31" t="n"/>
-      <c r="N82" s="31" t="n"/>
-      <c r="O82" s="31" t="n"/>
-      <c r="P82" s="31" t="n"/>
+      <c r="C82" s="80" t="n"/>
+      <c r="D82" s="80" t="n"/>
+      <c r="E82" s="80" t="n"/>
+      <c r="F82" s="80" t="n"/>
+      <c r="G82" s="80" t="n"/>
+      <c r="H82" s="80" t="n"/>
+      <c r="I82" s="80" t="n"/>
+      <c r="J82" s="80" t="n"/>
+      <c r="K82" s="80" t="n"/>
+      <c r="L82" s="80" t="n"/>
+      <c r="M82" s="80" t="n"/>
+      <c r="N82" s="80" t="n"/>
+      <c r="O82" s="80" t="n"/>
+      <c r="P82" s="80" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14590,25 +14849,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B83" s="20" t="inlineStr">
+      <c r="B83" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C83" s="31" t="n"/>
-      <c r="D83" s="31" t="n"/>
-      <c r="E83" s="31" t="n"/>
-      <c r="F83" s="31" t="n"/>
-      <c r="G83" s="31" t="n"/>
-      <c r="H83" s="31" t="n"/>
-      <c r="I83" s="31" t="n"/>
-      <c r="J83" s="31" t="n"/>
-      <c r="K83" s="31" t="n"/>
-      <c r="L83" s="31" t="n"/>
-      <c r="M83" s="31" t="n"/>
-      <c r="N83" s="31" t="n"/>
-      <c r="O83" s="31" t="n"/>
-      <c r="P83" s="31" t="n"/>
+      <c r="C83" s="80" t="n"/>
+      <c r="D83" s="80" t="n"/>
+      <c r="E83" s="80" t="n"/>
+      <c r="F83" s="80" t="n"/>
+      <c r="G83" s="80" t="n"/>
+      <c r="H83" s="80" t="n"/>
+      <c r="I83" s="80" t="n"/>
+      <c r="J83" s="80" t="n"/>
+      <c r="K83" s="80" t="n"/>
+      <c r="L83" s="80" t="n"/>
+      <c r="M83" s="80" t="n"/>
+      <c r="N83" s="80" t="n"/>
+      <c r="O83" s="80" t="n"/>
+      <c r="P83" s="80" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="33">
       <c r="A84" t="inlineStr">
@@ -14616,25 +14875,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B84" s="81" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="31" t="n"/>
-      <c r="D84" s="31" t="n"/>
-      <c r="E84" s="31" t="n"/>
-      <c r="F84" s="31" t="n"/>
-      <c r="G84" s="31" t="n"/>
-      <c r="H84" s="31" t="n"/>
-      <c r="I84" s="31" t="n"/>
-      <c r="J84" s="31" t="n"/>
-      <c r="K84" s="31" t="n"/>
-      <c r="L84" s="31" t="n"/>
-      <c r="M84" s="31" t="n"/>
-      <c r="N84" s="31" t="n"/>
-      <c r="O84" s="31" t="n"/>
-      <c r="P84" s="31" t="n"/>
+      <c r="C84" s="80" t="n"/>
+      <c r="D84" s="80" t="n"/>
+      <c r="E84" s="80" t="n"/>
+      <c r="F84" s="80" t="n"/>
+      <c r="G84" s="80" t="n"/>
+      <c r="H84" s="80" t="n"/>
+      <c r="I84" s="80" t="n"/>
+      <c r="J84" s="80" t="n"/>
+      <c r="K84" s="80" t="n"/>
+      <c r="L84" s="80" t="n"/>
+      <c r="M84" s="80" t="n"/>
+      <c r="N84" s="80" t="n"/>
+      <c r="O84" s="80" t="n"/>
+      <c r="P84" s="80" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="33">
       <c r="C85" s="31" t="n"/>
@@ -14662,7 +14921,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -14776,25 +15044,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B89" s="20" t="inlineStr">
+      <c r="B89" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="21" t="n"/>
-      <c r="K89" s="21" t="n"/>
-      <c r="L89" s="21" t="n"/>
-      <c r="M89" s="21" t="n"/>
-      <c r="N89" s="21" t="n"/>
-      <c r="O89" s="21" t="n"/>
-      <c r="P89" s="21" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="n"/>
+      <c r="F89" s="82" t="n"/>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="n"/>
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="n"/>
+      <c r="L89" s="82" t="n"/>
+      <c r="M89" s="82" t="n"/>
+      <c r="N89" s="82" t="n"/>
+      <c r="O89" s="82" t="n"/>
+      <c r="P89" s="82" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14802,25 +15070,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B90" s="20" t="inlineStr">
+      <c r="B90" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="21" t="n"/>
-      <c r="K90" s="21" t="n"/>
-      <c r="L90" s="21" t="n"/>
-      <c r="M90" s="21" t="n"/>
-      <c r="N90" s="21" t="n"/>
-      <c r="O90" s="21" t="n"/>
-      <c r="P90" s="21" t="n"/>
+      <c r="C90" s="82" t="n"/>
+      <c r="D90" s="82" t="n"/>
+      <c r="E90" s="82" t="n"/>
+      <c r="F90" s="82" t="n"/>
+      <c r="G90" s="82" t="n"/>
+      <c r="H90" s="82" t="n"/>
+      <c r="I90" s="82" t="n"/>
+      <c r="J90" s="82" t="n"/>
+      <c r="K90" s="82" t="n"/>
+      <c r="L90" s="82" t="n"/>
+      <c r="M90" s="82" t="n"/>
+      <c r="N90" s="82" t="n"/>
+      <c r="O90" s="82" t="n"/>
+      <c r="P90" s="82" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14828,25 +15096,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B91" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="21" t="n"/>
-      <c r="K91" s="21" t="n"/>
-      <c r="L91" s="21" t="n"/>
-      <c r="M91" s="21" t="n"/>
-      <c r="N91" s="21" t="n"/>
-      <c r="O91" s="21" t="n"/>
-      <c r="P91" s="21" t="n"/>
+      <c r="C91" s="82" t="n"/>
+      <c r="D91" s="82" t="n"/>
+      <c r="E91" s="82" t="n"/>
+      <c r="F91" s="82" t="n"/>
+      <c r="G91" s="82" t="n"/>
+      <c r="H91" s="82" t="n"/>
+      <c r="I91" s="82" t="n"/>
+      <c r="J91" s="82" t="n"/>
+      <c r="K91" s="82" t="n"/>
+      <c r="L91" s="82" t="n"/>
+      <c r="M91" s="82" t="n"/>
+      <c r="N91" s="82" t="n"/>
+      <c r="O91" s="82" t="n"/>
+      <c r="P91" s="82" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14854,25 +15122,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B92" s="20" t="inlineStr">
+      <c r="B92" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="J92" s="21" t="n"/>
-      <c r="K92" s="21" t="n"/>
-      <c r="L92" s="21" t="n"/>
-      <c r="M92" s="21" t="n"/>
-      <c r="N92" s="21" t="n"/>
-      <c r="O92" s="21" t="n"/>
-      <c r="P92" s="21" t="n"/>
+      <c r="C92" s="82" t="n"/>
+      <c r="D92" s="82" t="n"/>
+      <c r="E92" s="82" t="n"/>
+      <c r="F92" s="82" t="n"/>
+      <c r="G92" s="82" t="n"/>
+      <c r="H92" s="82" t="n"/>
+      <c r="I92" s="82" t="n"/>
+      <c r="J92" s="82" t="n"/>
+      <c r="K92" s="82" t="n"/>
+      <c r="L92" s="82" t="n"/>
+      <c r="M92" s="82" t="n"/>
+      <c r="N92" s="82" t="n"/>
+      <c r="O92" s="82" t="n"/>
+      <c r="P92" s="82" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14880,25 +15148,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B93" s="20" t="inlineStr">
+      <c r="B93" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="21" t="n"/>
-      <c r="K93" s="21" t="n"/>
-      <c r="L93" s="21" t="n"/>
-      <c r="M93" s="21" t="n"/>
-      <c r="N93" s="21" t="n"/>
-      <c r="O93" s="21" t="n"/>
-      <c r="P93" s="21" t="n"/>
+      <c r="C93" s="82" t="n"/>
+      <c r="D93" s="82" t="n"/>
+      <c r="E93" s="82" t="n"/>
+      <c r="F93" s="82" t="n"/>
+      <c r="G93" s="82" t="n"/>
+      <c r="H93" s="82" t="n"/>
+      <c r="I93" s="82" t="n"/>
+      <c r="J93" s="82" t="n"/>
+      <c r="K93" s="82" t="n"/>
+      <c r="L93" s="82" t="n"/>
+      <c r="M93" s="82" t="n"/>
+      <c r="N93" s="82" t="n"/>
+      <c r="O93" s="82" t="n"/>
+      <c r="P93" s="82" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14906,25 +15174,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B94" s="20" t="inlineStr">
+      <c r="B94" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="21" t="n"/>
-      <c r="K94" s="21" t="n"/>
-      <c r="L94" s="21" t="n"/>
-      <c r="M94" s="21" t="n"/>
-      <c r="N94" s="21" t="n"/>
-      <c r="O94" s="21" t="n"/>
-      <c r="P94" s="21" t="n"/>
+      <c r="C94" s="82" t="n"/>
+      <c r="D94" s="82" t="n"/>
+      <c r="E94" s="82" t="n"/>
+      <c r="F94" s="82" t="n"/>
+      <c r="G94" s="82" t="n"/>
+      <c r="H94" s="82" t="n"/>
+      <c r="I94" s="82" t="n"/>
+      <c r="J94" s="82" t="n"/>
+      <c r="K94" s="82" t="n"/>
+      <c r="L94" s="82" t="n"/>
+      <c r="M94" s="82" t="n"/>
+      <c r="N94" s="82" t="n"/>
+      <c r="O94" s="82" t="n"/>
+      <c r="P94" s="82" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14932,25 +15200,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B95" s="79" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="21" t="n"/>
-      <c r="K95" s="21" t="n"/>
-      <c r="L95" s="21" t="n"/>
-      <c r="M95" s="21" t="n"/>
-      <c r="N95" s="21" t="n"/>
-      <c r="O95" s="21" t="n"/>
-      <c r="P95" s="21" t="n"/>
+      <c r="C95" s="82" t="n"/>
+      <c r="D95" s="82" t="n"/>
+      <c r="E95" s="82" t="n"/>
+      <c r="F95" s="82" t="n"/>
+      <c r="G95" s="82" t="n"/>
+      <c r="H95" s="82" t="n"/>
+      <c r="I95" s="82" t="n"/>
+      <c r="J95" s="82" t="n"/>
+      <c r="K95" s="82" t="n"/>
+      <c r="L95" s="82" t="n"/>
+      <c r="M95" s="82" t="n"/>
+      <c r="N95" s="82" t="n"/>
+      <c r="O95" s="82" t="n"/>
+      <c r="P95" s="82" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="33">
       <c r="A96" t="inlineStr">
@@ -14958,84 +15226,84 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B96" s="28" t="inlineStr">
+      <c r="B96" s="81" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="21" t="n"/>
-      <c r="K96" s="21" t="n"/>
-      <c r="L96" s="21" t="n"/>
-      <c r="M96" s="21" t="n"/>
-      <c r="N96" s="21" t="n"/>
-      <c r="O96" s="21" t="n"/>
-      <c r="P96" s="21" t="n"/>
+      <c r="C96" s="82" t="n"/>
+      <c r="D96" s="82" t="n"/>
+      <c r="E96" s="82" t="n"/>
+      <c r="F96" s="82" t="n"/>
+      <c r="G96" s="82" t="n"/>
+      <c r="H96" s="82" t="n"/>
+      <c r="I96" s="82" t="n"/>
+      <c r="J96" s="82" t="n"/>
+      <c r="K96" s="82" t="n"/>
+      <c r="L96" s="82" t="n"/>
+      <c r="M96" s="82" t="n"/>
+      <c r="N96" s="82" t="n"/>
+      <c r="O96" s="82" t="n"/>
+      <c r="P96" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15078,9 +15346,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -15422,9 +15697,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -15766,9 +16048,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="6" t="n"/>
@@ -15965,37 +16254,39 @@
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="31" t="n">
-        <v>9</v>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
       </c>
       <c r="D32" s="31" t="inlineStr">
         <is>
-          <t>1.8, 1.9, 1.10, 10, 11</t>
+          <t>Q1.8, Q1.9, Q1.10, Q10, Q11</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>1.3, 2, 3, 4</t>
+          <t>Q1.3, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="F32" s="31" t="inlineStr">
         <is>
-          <t>1.2, 5</t>
+          <t>Q1.2, Q5</t>
         </is>
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 1.7, 6, 7, 8</t>
+          <t>Q1.5, Q1.6, Q1.7, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="H32" s="31" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Q1.1</t>
         </is>
       </c>
       <c r="I32" s="31" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>Q1.4</t>
         </is>
       </c>
       <c r="J32" s="31" t="n"/>
@@ -16136,9 +16427,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -16480,9 +16778,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="6" t="n"/>
@@ -16655,24 +16960,26 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>1.5, 1.6, 6</t>
+          <t>Q1.5, Q1.6, Q6</t>
         </is>
       </c>
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="31" t="n"/>
       <c r="G55" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="H55" s="31" t="n"/>
-      <c r="I55" s="31" t="n">
-        <v>4</v>
+      <c r="I55" s="31" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
       </c>
       <c r="J55" s="31" t="n"/>
       <c r="K55" s="31" t="n"/>
@@ -16721,25 +17028,25 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>1.5, 5</t>
+          <t>Q1.5, Q5</t>
         </is>
       </c>
       <c r="D57" s="31" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6, 7</t>
+          <t>Q1.6, Q1.7, Q6, Q7</t>
         </is>
       </c>
       <c r="E57" s="31" t="n"/>
       <c r="F57" s="31" t="n"/>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q2, Q3</t>
         </is>
       </c>
       <c r="H57" s="31" t="n"/>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>1.4, 4</t>
+          <t>Q1.4, Q4</t>
         </is>
       </c>
       <c r="J57" s="31" t="n"/>
@@ -16756,25 +17063,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16854,9 +17161,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -17029,23 +17343,23 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 2, 5.1</t>
+          <t>Q1.1, Q1.2, Q2, Q5.1</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 3, 4, 6</t>
+          <t>Q1.3, Q1.4, Q1.5, Q3, Q4, Q6</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 7</t>
+          <t>Q1.6, Q1.7, Q7</t>
         </is>
       </c>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>(5.2-5.4)</t>
+          <t>Q5.2-5.4</t>
         </is>
       </c>
       <c r="H67" s="21" t="n"/>
@@ -17071,23 +17385,23 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.7, 2</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.7, Q2</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>1.4, 1.6, 4, 5, 8</t>
+          <t>Q1.4, Q1.6, Q4, Q5, Q8</t>
         </is>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>6, 7</t>
+          <t>Q6, Q7</t>
         </is>
       </c>
       <c r="F68" s="21" t="n"/>
       <c r="G68" s="21" t="inlineStr">
         <is>
-          <t>1.5, 3</t>
+          <t>Q1.5, Q3</t>
         </is>
       </c>
       <c r="H68" s="21" t="n"/>
@@ -17132,25 +17446,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17230,9 +17544,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="6" t="n"/>
@@ -17461,7 +17782,7 @@
       <c r="F81" s="31" t="n"/>
       <c r="G81" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 2, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q2, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="H81" s="31" t="n"/>
@@ -17491,7 +17812,7 @@
       <c r="F82" s="31" t="n"/>
       <c r="G82" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 2, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q2, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="H82" s="31" t="n"/>
@@ -17582,9 +17903,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -17809,12 +18137,12 @@
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>1.1, 2, 3</t>
+          <t>Q1.1, Q2, Q3</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 4, 5</t>
+          <t>Q1.2, Q1.3, Q4, Q5</t>
         </is>
       </c>
       <c r="E93" s="21" t="n"/>
@@ -17843,12 +18171,12 @@
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 2.2, 3</t>
+          <t>Q1.1, Q1.2, Q2.2, Q3</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>1.3, 2.1, 4, 5</t>
+          <t>Q1.3, Q2.1, Q4, Q5</t>
         </is>
       </c>
       <c r="E94" s="21" t="n"/>
@@ -17919,61 +18247,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18016,9 +18344,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -18360,9 +18695,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -18704,9 +19046,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -19048,9 +19397,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -19392,9 +19748,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -19567,25 +19930,25 @@
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>1.7, 5</t>
+          <t>Q1.7, Q5</t>
         </is>
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>1.8, 1.9, 1.10, 6</t>
+          <t>Q1.8, Q1.9, Q1.10, Q6</t>
         </is>
       </c>
       <c r="E55" s="31" t="n"/>
       <c r="F55" s="31" t="n"/>
       <c r="G55" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.4, 1.5, 2, 3</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.4, Q1.5, Q2, Q3</t>
         </is>
       </c>
       <c r="H55" s="31" t="n"/>
       <c r="I55" s="31" t="inlineStr">
         <is>
-          <t>1.6, 4</t>
+          <t>Q1.6, Q4</t>
         </is>
       </c>
       <c r="J55" s="31" t="n"/>
@@ -19609,25 +19972,25 @@
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D56" s="31" t="inlineStr">
         <is>
-          <t>1.2, 1.8, 1.9, 1.10, 7</t>
+          <t>Q1.2, Q1.8, Q1.9, Q1.10, Q7</t>
         </is>
       </c>
       <c r="E56" s="31" t="n"/>
       <c r="F56" s="31" t="n"/>
       <c r="G56" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.3, 1.5, 1.6, 2, 3, 6</t>
+          <t>Q1.1, Q1.3, Q1.5, Q1.6, Q2, Q3, Q6</t>
         </is>
       </c>
       <c r="H56" s="31" t="n"/>
       <c r="I56" s="31" t="inlineStr">
         <is>
-          <t>1.7, 4</t>
+          <t>Q1.7, Q4</t>
         </is>
       </c>
       <c r="J56" s="31" t="n"/>
@@ -19651,25 +20014,25 @@
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>1.4, 5</t>
+          <t>Q1.4, Q5</t>
         </is>
       </c>
       <c r="D57" s="31" t="inlineStr">
         <is>
-          <t>1.6, 1.7, 6</t>
+          <t>Q1.6, Q1.7, Q6</t>
         </is>
       </c>
       <c r="E57" s="31" t="n"/>
       <c r="F57" s="31" t="n"/>
       <c r="G57" s="31" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.3, 1.8, 1.9, 1.10, 2, 3, 4</t>
+          <t>Q1.1, Q1.2, Q1.3, Q1.8, Q1.9, Q1.10, Q2, Q3, Q4</t>
         </is>
       </c>
       <c r="H57" s="31" t="n"/>
       <c r="I57" s="31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>Q1.5</t>
         </is>
       </c>
       <c r="J57" s="31" t="n"/>
@@ -19686,25 +20049,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19784,9 +20147,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -19959,19 +20329,19 @@
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>1.3, 1.4, 1.5, 1.9, 2</t>
+          <t>Q1.3, Q1.4, Q1.5, Q1.9, Q2</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.2, 1.6, 1.7, 1.8, 3, 4, 5</t>
+          <t>Q1.1, Q1.2, Q1.6, Q1.7, Q1.8, Q3, Q4, Q5</t>
         </is>
       </c>
       <c r="E67" s="21" t="n"/>
       <c r="F67" s="21" t="n"/>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>1.10, 6</t>
+          <t>Q1.10, Q6</t>
         </is>
       </c>
       <c r="H67" s="21" t="n"/>
@@ -19997,18 +20367,20 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>1.1, 1.4, 2, 3</t>
+          <t>Q1.1, Q1.4, Q2, Q3</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>1.2, 1.3, 1.5, 1.6, 1.7, 1.9, 1.10, 4, 5, 6, 8</t>
+          <t>Q1.2, Q1.3, Q1.5, Q1.6, Q1.7, Q1.9, Q1.10, Q4, Q5, Q6, Q8</t>
         </is>
       </c>
       <c r="E68" s="21" t="n"/>
       <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n">
-        <v>7</v>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
       </c>
       <c r="H68" s="21" t="n"/>
       <c r="I68" s="21" t="n"/>
@@ -20052,25 +20424,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20150,9 +20522,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -20494,9 +20873,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -20864,61 +21250,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20961,9 +21347,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -21305,9 +21698,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -21649,9 +22049,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -21993,9 +22400,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -22337,9 +22751,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -22583,25 +23004,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22681,9 +23102,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -22927,25 +23355,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23025,9 +23453,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -23369,9 +23804,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -23706,61 +24148,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23803,7 +24245,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3">
       <c r="B3" s="6" t="n"/>
@@ -23917,25 +24368,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="J5" s="21" t="n"/>
-      <c r="K5" s="21" t="n"/>
-      <c r="L5" s="21" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
-      <c r="P5" s="21" t="n"/>
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="82" t="n"/>
+      <c r="E5" s="82" t="n"/>
+      <c r="F5" s="82" t="n"/>
+      <c r="G5" s="82" t="n"/>
+      <c r="H5" s="82" t="n"/>
+      <c r="I5" s="82" t="n"/>
+      <c r="J5" s="82" t="n"/>
+      <c r="K5" s="82" t="n"/>
+      <c r="L5" s="82" t="n"/>
+      <c r="M5" s="82" t="n"/>
+      <c r="N5" s="82" t="n"/>
+      <c r="O5" s="82" t="n"/>
+      <c r="P5" s="82" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23943,25 +24394,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="21" t="n"/>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="F6" s="21" t="n"/>
-      <c r="G6" s="21" t="n"/>
-      <c r="H6" s="21" t="n"/>
-      <c r="I6" s="21" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n"/>
-      <c r="L6" s="21" t="n"/>
-      <c r="M6" s="21" t="n"/>
-      <c r="N6" s="21" t="n"/>
-      <c r="O6" s="21" t="n"/>
-      <c r="P6" s="21" t="n"/>
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="82" t="n"/>
+      <c r="F6" s="82" t="n"/>
+      <c r="G6" s="82" t="n"/>
+      <c r="H6" s="82" t="n"/>
+      <c r="I6" s="82" t="n"/>
+      <c r="J6" s="82" t="n"/>
+      <c r="K6" s="82" t="n"/>
+      <c r="L6" s="82" t="n"/>
+      <c r="M6" s="82" t="n"/>
+      <c r="N6" s="82" t="n"/>
+      <c r="O6" s="82" t="n"/>
+      <c r="P6" s="82" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23969,25 +24420,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
+      <c r="C7" s="82" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="82" t="n"/>
+      <c r="F7" s="82" t="n"/>
+      <c r="G7" s="82" t="n"/>
+      <c r="H7" s="82" t="n"/>
+      <c r="I7" s="82" t="n"/>
+      <c r="J7" s="82" t="n"/>
+      <c r="K7" s="82" t="n"/>
+      <c r="L7" s="82" t="n"/>
+      <c r="M7" s="82" t="n"/>
+      <c r="N7" s="82" t="n"/>
+      <c r="O7" s="82" t="n"/>
+      <c r="P7" s="82" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23995,25 +24446,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
+      <c r="C8" s="82" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="82" t="n"/>
+      <c r="F8" s="82" t="n"/>
+      <c r="G8" s="82" t="n"/>
+      <c r="H8" s="82" t="n"/>
+      <c r="I8" s="82" t="n"/>
+      <c r="J8" s="82" t="n"/>
+      <c r="K8" s="82" t="n"/>
+      <c r="L8" s="82" t="n"/>
+      <c r="M8" s="82" t="n"/>
+      <c r="N8" s="82" t="n"/>
+      <c r="O8" s="82" t="n"/>
+      <c r="P8" s="82" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24021,25 +24472,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
+      <c r="C9" s="82" t="n"/>
+      <c r="D9" s="82" t="n"/>
+      <c r="E9" s="82" t="n"/>
+      <c r="F9" s="82" t="n"/>
+      <c r="G9" s="82" t="n"/>
+      <c r="H9" s="82" t="n"/>
+      <c r="I9" s="82" t="n"/>
+      <c r="J9" s="82" t="n"/>
+      <c r="K9" s="82" t="n"/>
+      <c r="L9" s="82" t="n"/>
+      <c r="M9" s="82" t="n"/>
+      <c r="N9" s="82" t="n"/>
+      <c r="O9" s="82" t="n"/>
+      <c r="P9" s="82" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24047,25 +24498,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
-      <c r="P10" s="21" t="n"/>
+      <c r="C10" s="82" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="82" t="n"/>
+      <c r="F10" s="82" t="n"/>
+      <c r="G10" s="82" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="82" t="n"/>
+      <c r="J10" s="82" t="n"/>
+      <c r="K10" s="82" t="n"/>
+      <c r="L10" s="82" t="n"/>
+      <c r="M10" s="82" t="n"/>
+      <c r="N10" s="82" t="n"/>
+      <c r="O10" s="82" t="n"/>
+      <c r="P10" s="82" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24073,25 +24524,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
+      <c r="G11" s="82" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="82" t="n"/>
+      <c r="J11" s="82" t="n"/>
+      <c r="K11" s="82" t="n"/>
+      <c r="L11" s="82" t="n"/>
+      <c r="M11" s="82" t="n"/>
+      <c r="N11" s="82" t="n"/>
+      <c r="O11" s="82" t="n"/>
+      <c r="P11" s="82" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="33">
       <c r="A12" t="inlineStr">
@@ -24099,25 +24550,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
-      <c r="P12" s="21" t="n"/>
+      <c r="C12" s="82" t="n"/>
+      <c r="D12" s="82" t="n"/>
+      <c r="E12" s="82" t="n"/>
+      <c r="F12" s="82" t="n"/>
+      <c r="G12" s="82" t="n"/>
+      <c r="H12" s="82" t="n"/>
+      <c r="I12" s="82" t="n"/>
+      <c r="J12" s="82" t="n"/>
+      <c r="K12" s="82" t="n"/>
+      <c r="L12" s="82" t="n"/>
+      <c r="M12" s="82" t="n"/>
+      <c r="N12" s="82" t="n"/>
+      <c r="O12" s="82" t="n"/>
+      <c r="P12" s="82" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="C13" s="21" t="n"/>
@@ -24145,7 +24596,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -24259,25 +24719,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="79" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
+      <c r="C17" s="82" t="n"/>
+      <c r="D17" s="82" t="n"/>
+      <c r="E17" s="82" t="n"/>
+      <c r="F17" s="82" t="n"/>
+      <c r="G17" s="82" t="n"/>
+      <c r="H17" s="82" t="n"/>
+      <c r="I17" s="82" t="n"/>
+      <c r="J17" s="82" t="n"/>
+      <c r="K17" s="82" t="n"/>
+      <c r="L17" s="82" t="n"/>
+      <c r="M17" s="82" t="n"/>
+      <c r="N17" s="82" t="n"/>
+      <c r="O17" s="82" t="n"/>
+      <c r="P17" s="82" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24285,25 +24745,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="83" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
+      <c r="C18" s="82" t="n"/>
+      <c r="D18" s="82" t="n"/>
+      <c r="E18" s="82" t="n"/>
+      <c r="F18" s="82" t="n"/>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="n"/>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="n"/>
+      <c r="M18" s="82" t="n"/>
+      <c r="N18" s="82" t="n"/>
+      <c r="O18" s="82" t="n"/>
+      <c r="P18" s="82" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24311,25 +24771,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="79" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
+      <c r="C19" s="82" t="n"/>
+      <c r="D19" s="82" t="n"/>
+      <c r="E19" s="82" t="n"/>
+      <c r="F19" s="82" t="n"/>
+      <c r="G19" s="82" t="n"/>
+      <c r="H19" s="82" t="n"/>
+      <c r="I19" s="82" t="n"/>
+      <c r="J19" s="82" t="n"/>
+      <c r="K19" s="82" t="n"/>
+      <c r="L19" s="82" t="n"/>
+      <c r="M19" s="82" t="n"/>
+      <c r="N19" s="82" t="n"/>
+      <c r="O19" s="82" t="n"/>
+      <c r="P19" s="82" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24337,25 +24797,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
+      <c r="C20" s="82" t="n"/>
+      <c r="D20" s="82" t="n"/>
+      <c r="E20" s="82" t="n"/>
+      <c r="F20" s="82" t="n"/>
+      <c r="G20" s="82" t="n"/>
+      <c r="H20" s="82" t="n"/>
+      <c r="I20" s="82" t="n"/>
+      <c r="J20" s="82" t="n"/>
+      <c r="K20" s="82" t="n"/>
+      <c r="L20" s="82" t="n"/>
+      <c r="M20" s="82" t="n"/>
+      <c r="N20" s="82" t="n"/>
+      <c r="O20" s="82" t="n"/>
+      <c r="P20" s="82" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24363,25 +24823,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="79" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
+      <c r="C21" s="82" t="n"/>
+      <c r="D21" s="82" t="n"/>
+      <c r="E21" s="82" t="n"/>
+      <c r="F21" s="82" t="n"/>
+      <c r="G21" s="82" t="n"/>
+      <c r="H21" s="82" t="n"/>
+      <c r="I21" s="82" t="n"/>
+      <c r="J21" s="82" t="n"/>
+      <c r="K21" s="82" t="n"/>
+      <c r="L21" s="82" t="n"/>
+      <c r="M21" s="82" t="n"/>
+      <c r="N21" s="82" t="n"/>
+      <c r="O21" s="82" t="n"/>
+      <c r="P21" s="82" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24389,25 +24849,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="79" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
+      <c r="C22" s="82" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="82" t="n"/>
+      <c r="F22" s="82" t="n"/>
+      <c r="G22" s="82" t="n"/>
+      <c r="H22" s="82" t="n"/>
+      <c r="I22" s="82" t="n"/>
+      <c r="J22" s="82" t="n"/>
+      <c r="K22" s="82" t="n"/>
+      <c r="L22" s="82" t="n"/>
+      <c r="M22" s="82" t="n"/>
+      <c r="N22" s="82" t="n"/>
+      <c r="O22" s="82" t="n"/>
+      <c r="P22" s="82" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24415,25 +24875,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="79" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
+      <c r="C23" s="82" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="82" t="n"/>
+      <c r="F23" s="82" t="n"/>
+      <c r="G23" s="82" t="n"/>
+      <c r="H23" s="82" t="n"/>
+      <c r="I23" s="82" t="n"/>
+      <c r="J23" s="82" t="n"/>
+      <c r="K23" s="82" t="n"/>
+      <c r="L23" s="82" t="n"/>
+      <c r="M23" s="82" t="n"/>
+      <c r="N23" s="82" t="n"/>
+      <c r="O23" s="82" t="n"/>
+      <c r="P23" s="82" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="33">
       <c r="A24" t="inlineStr">
@@ -24441,39 +24901,39 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B24" s="81" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="82" t="n"/>
+      <c r="E24" s="82" t="n"/>
+      <c r="F24" s="82" t="n"/>
+      <c r="G24" s="82" t="n"/>
+      <c r="H24" s="82" t="n"/>
+      <c r="I24" s="82" t="n"/>
+      <c r="J24" s="82" t="n"/>
+      <c r="K24" s="82" t="n"/>
+      <c r="L24" s="82" t="n"/>
+      <c r="M24" s="82" t="n"/>
+      <c r="N24" s="82" t="n"/>
+      <c r="O24" s="82" t="n"/>
+      <c r="P24" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B2:G2"/>
     <mergeCell ref="N15:P15"/>
-    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D3:F3"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="B15:B16"/>
@@ -24519,9 +24979,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -24863,9 +25330,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -25207,9 +25681,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -25551,9 +26032,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -25895,9 +26383,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -26141,25 +26636,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26239,9 +26734,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -26485,25 +26987,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26583,9 +27085,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -26927,9 +27436,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -27280,61 +27796,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27377,9 +27893,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -27721,9 +28244,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -28065,9 +28595,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -28409,9 +28946,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -28753,9 +29297,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -28999,25 +29550,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -29097,9 +29648,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -29343,25 +29901,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -29441,9 +29999,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -29785,9 +30350,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -30122,61 +30694,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30219,9 +30791,16 @@
       <c r="D2" s="70" t="n"/>
       <c r="E2" s="70" t="n"/>
       <c r="F2" s="70" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
+      <c r="G2" s="70" t="n"/>
+      <c r="H2" s="70" t="n"/>
+      <c r="I2" s="70" t="n"/>
+      <c r="J2" s="70" t="n"/>
+      <c r="K2" s="70" t="n"/>
+      <c r="L2" s="70" t="n"/>
+      <c r="M2" s="70" t="n"/>
+      <c r="N2" s="70" t="n"/>
+      <c r="O2" s="70" t="n"/>
+      <c r="P2" s="71" t="n"/>
     </row>
     <row r="3" ht="14.3" customHeight="1" s="33">
       <c r="B3" s="6" t="n"/>
@@ -30563,9 +31142,16 @@
       <c r="D14" s="70" t="n"/>
       <c r="E14" s="70" t="n"/>
       <c r="F14" s="70" t="n"/>
-      <c r="G14" s="71" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
+      <c r="G14" s="70" t="n"/>
+      <c r="H14" s="70" t="n"/>
+      <c r="I14" s="70" t="n"/>
+      <c r="J14" s="70" t="n"/>
+      <c r="K14" s="70" t="n"/>
+      <c r="L14" s="70" t="n"/>
+      <c r="M14" s="70" t="n"/>
+      <c r="N14" s="70" t="n"/>
+      <c r="O14" s="70" t="n"/>
+      <c r="P14" s="71" t="n"/>
     </row>
     <row r="15" ht="14.3" customHeight="1" s="33">
       <c r="B15" s="6" t="n"/>
@@ -30907,9 +31493,16 @@
       <c r="D26" s="70" t="n"/>
       <c r="E26" s="70" t="n"/>
       <c r="F26" s="70" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
+      <c r="G26" s="70" t="n"/>
+      <c r="H26" s="70" t="n"/>
+      <c r="I26" s="70" t="n"/>
+      <c r="J26" s="70" t="n"/>
+      <c r="K26" s="70" t="n"/>
+      <c r="L26" s="70" t="n"/>
+      <c r="M26" s="70" t="n"/>
+      <c r="N26" s="70" t="n"/>
+      <c r="O26" s="70" t="n"/>
+      <c r="P26" s="71" t="n"/>
     </row>
     <row r="27" ht="14.3" customHeight="1" s="33">
       <c r="B27" s="6" t="n"/>
@@ -31251,9 +31844,16 @@
       <c r="D38" s="70" t="n"/>
       <c r="E38" s="70" t="n"/>
       <c r="F38" s="70" t="n"/>
-      <c r="G38" s="71" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
+      <c r="G38" s="70" t="n"/>
+      <c r="H38" s="70" t="n"/>
+      <c r="I38" s="70" t="n"/>
+      <c r="J38" s="70" t="n"/>
+      <c r="K38" s="70" t="n"/>
+      <c r="L38" s="70" t="n"/>
+      <c r="M38" s="70" t="n"/>
+      <c r="N38" s="70" t="n"/>
+      <c r="O38" s="70" t="n"/>
+      <c r="P38" s="71" t="n"/>
     </row>
     <row r="39" ht="14.3" customHeight="1" s="33">
       <c r="B39" s="6" t="n"/>
@@ -31595,9 +32195,16 @@
       <c r="D50" s="70" t="n"/>
       <c r="E50" s="70" t="n"/>
       <c r="F50" s="70" t="n"/>
-      <c r="G50" s="71" t="n"/>
-      <c r="J50" s="5" t="n"/>
-      <c r="K50" s="5" t="n"/>
+      <c r="G50" s="70" t="n"/>
+      <c r="H50" s="70" t="n"/>
+      <c r="I50" s="70" t="n"/>
+      <c r="J50" s="70" t="n"/>
+      <c r="K50" s="70" t="n"/>
+      <c r="L50" s="70" t="n"/>
+      <c r="M50" s="70" t="n"/>
+      <c r="N50" s="70" t="n"/>
+      <c r="O50" s="70" t="n"/>
+      <c r="P50" s="71" t="n"/>
     </row>
     <row r="51" ht="14.3" customHeight="1" s="33">
       <c r="B51" s="6" t="n"/>
@@ -31841,25 +32448,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="31" t="n"/>
-      <c r="D58" s="31" t="n"/>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="31" t="n"/>
-      <c r="J58" s="31" t="n"/>
-      <c r="K58" s="31" t="n"/>
-      <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="31" t="n"/>
-      <c r="O58" s="31" t="n"/>
-      <c r="P58" s="31" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="80" t="n"/>
+      <c r="E58" s="80" t="n"/>
+      <c r="F58" s="80" t="n"/>
+      <c r="G58" s="80" t="n"/>
+      <c r="H58" s="80" t="n"/>
+      <c r="I58" s="80" t="n"/>
+      <c r="J58" s="80" t="n"/>
+      <c r="K58" s="80" t="n"/>
+      <c r="L58" s="80" t="n"/>
+      <c r="M58" s="80" t="n"/>
+      <c r="N58" s="80" t="n"/>
+      <c r="O58" s="80" t="n"/>
+      <c r="P58" s="80" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -31939,9 +32546,16 @@
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="70" t="n"/>
       <c r="F62" s="70" t="n"/>
-      <c r="G62" s="71" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
+      <c r="G62" s="70" t="n"/>
+      <c r="H62" s="70" t="n"/>
+      <c r="I62" s="70" t="n"/>
+      <c r="J62" s="70" t="n"/>
+      <c r="K62" s="70" t="n"/>
+      <c r="L62" s="70" t="n"/>
+      <c r="M62" s="70" t="n"/>
+      <c r="N62" s="70" t="n"/>
+      <c r="O62" s="70" t="n"/>
+      <c r="P62" s="71" t="n"/>
     </row>
     <row r="63" ht="14.3" customHeight="1" s="33">
       <c r="B63" s="6" t="n"/>
@@ -32185,25 +32799,25 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="79" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="21" t="n"/>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="21" t="n"/>
-      <c r="F70" s="21" t="n"/>
-      <c r="G70" s="21" t="n"/>
-      <c r="H70" s="21" t="n"/>
-      <c r="I70" s="21" t="n"/>
-      <c r="J70" s="21" t="n"/>
-      <c r="K70" s="21" t="n"/>
-      <c r="L70" s="21" t="n"/>
-      <c r="M70" s="21" t="n"/>
-      <c r="N70" s="21" t="n"/>
-      <c r="O70" s="21" t="n"/>
-      <c r="P70" s="21" t="n"/>
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="82" t="n"/>
+      <c r="E70" s="82" t="n"/>
+      <c r="F70" s="82" t="n"/>
+      <c r="G70" s="82" t="n"/>
+      <c r="H70" s="82" t="n"/>
+      <c r="I70" s="82" t="n"/>
+      <c r="J70" s="82" t="n"/>
+      <c r="K70" s="82" t="n"/>
+      <c r="L70" s="82" t="n"/>
+      <c r="M70" s="82" t="n"/>
+      <c r="N70" s="82" t="n"/>
+      <c r="O70" s="82" t="n"/>
+      <c r="P70" s="82" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -32283,9 +32897,16 @@
       <c r="D74" s="70" t="n"/>
       <c r="E74" s="70" t="n"/>
       <c r="F74" s="70" t="n"/>
-      <c r="G74" s="71" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="5" t="n"/>
+      <c r="G74" s="70" t="n"/>
+      <c r="H74" s="70" t="n"/>
+      <c r="I74" s="70" t="n"/>
+      <c r="J74" s="70" t="n"/>
+      <c r="K74" s="70" t="n"/>
+      <c r="L74" s="70" t="n"/>
+      <c r="M74" s="70" t="n"/>
+      <c r="N74" s="70" t="n"/>
+      <c r="O74" s="70" t="n"/>
+      <c r="P74" s="71" t="n"/>
     </row>
     <row r="75" ht="14.3" customHeight="1" s="33">
       <c r="B75" s="6" t="n"/>
@@ -32627,9 +33248,16 @@
       <c r="D86" s="70" t="n"/>
       <c r="E86" s="70" t="n"/>
       <c r="F86" s="70" t="n"/>
-      <c r="G86" s="71" t="n"/>
-      <c r="J86" s="5" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="G86" s="70" t="n"/>
+      <c r="H86" s="70" t="n"/>
+      <c r="I86" s="70" t="n"/>
+      <c r="J86" s="70" t="n"/>
+      <c r="K86" s="70" t="n"/>
+      <c r="L86" s="70" t="n"/>
+      <c r="M86" s="70" t="n"/>
+      <c r="N86" s="70" t="n"/>
+      <c r="O86" s="70" t="n"/>
+      <c r="P86" s="71" t="n"/>
     </row>
     <row r="87" ht="14.3" customHeight="1" s="33">
       <c r="B87" s="6" t="n"/>
@@ -32980,61 +33608,61 @@
   </sheetData>
   <mergeCells count="56">
     <mergeCell ref="J75:M75"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="B14:P14"/>
     <mergeCell ref="G87:I87"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="C63:C64"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="J51:M51"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="D87:F87"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B74:G74"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C75:C76"/>
+    <mergeCell ref="B38:P38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="N87:P87"/>
     <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="B74:P74"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="G63:I63"/>
     <mergeCell ref="D51:F51"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="B86:G86"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C75:C76"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="N87:P87"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G51:I51"/>
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C51:C52"/>
     <mergeCell ref="J87:M87"/>
     <mergeCell ref="G75:I75"/>
-    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B50:P50"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:B64"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="N63:P63"/>
     <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B75:B76"/>
     <mergeCell ref="G27:I27"/>
-    <mergeCell ref="C87:C88"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N75:P75"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="J63:M63"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B86:P86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
